--- a/data/costs.xlsx
+++ b/data/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Code2\1_PROJ_GROUPS\10_TrainGames\Subway Builder\Modding\subwaybuilder-uk-generic-trains\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAD787E-84E6-4E24-8D28-04EDE004141F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E769ACC-07C8-4060-8BBB-AEBCD2BA8ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train Running Costs" sheetId="1" r:id="rId1"/>
@@ -2393,40 +2393,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>663</c:v>
+                  <c:v>580</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>726</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>789</c:v>
+                  <c:v>680</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>852</c:v>
+                  <c:v>730</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>915</c:v>
+                  <c:v>780</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>978</c:v>
+                  <c:v>830</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1041</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1104</c:v>
+                  <c:v>930</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1167</c:v>
+                  <c:v>980</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1230</c:v>
+                  <c:v>1030</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1293</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1356</c:v>
+                  <c:v>1130</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3050,28 +3050,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>550</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>600</c:v>
+                  <c:v>545</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>650</c:v>
+                  <c:v>590</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>700</c:v>
+                  <c:v>635</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>680</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>800</c:v>
+                  <c:v>725</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>850</c:v>
+                  <c:v>770</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3667,28 +3667,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>550</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>600</c:v>
+                  <c:v>545</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>650</c:v>
+                  <c:v>590</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>700</c:v>
+                  <c:v>635</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>680</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>800</c:v>
+                  <c:v>725</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>850</c:v>
+                  <c:v>770</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3921,40 +3921,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>663</c:v>
+                  <c:v>580</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>726</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>789</c:v>
+                  <c:v>680</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>852</c:v>
+                  <c:v>730</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>915</c:v>
+                  <c:v>780</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>978</c:v>
+                  <c:v>830</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1041</c:v>
+                  <c:v>880</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1104</c:v>
+                  <c:v>930</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1167</c:v>
+                  <c:v>980</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1230</c:v>
+                  <c:v>1030</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1293</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1356</c:v>
+                  <c:v>1130</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="V3">
         <f>$B$9+G3*$C$9</f>
-        <v>663</v>
+        <v>580</v>
       </c>
       <c r="W3">
         <f>G3*$D$9</f>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="Z3">
         <f>$B$11+G3*$C$11</f>
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="AA3">
         <f>G3*$D$11</f>
@@ -7764,11 +7764,11 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H18" si="0">$B$2+G4*$C$2</f>
+        <f t="shared" ref="H4:H17" si="0">$B$2+G4*$C$2</f>
         <v>300</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I18" si="1">G4*$D$2</f>
+        <f t="shared" ref="I4:I17" si="1">G4*$D$2</f>
         <v>480</v>
       </c>
       <c r="J4">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="V4">
         <f t="shared" ref="V4:V14" si="14">$B$9+G4*$C$9</f>
-        <v>726</v>
+        <v>630</v>
       </c>
       <c r="W4">
         <f t="shared" ref="W4:W14" si="15">G4*$D$9</f>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="Z4">
         <f t="shared" ref="Z4:Z10" si="18">$B$11+G4*$C$11</f>
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="AA4">
         <f t="shared" ref="AA4:AA10" si="19">G4*$D$11</f>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="V5">
         <f t="shared" si="14"/>
-        <v>789</v>
+        <v>680</v>
       </c>
       <c r="W5">
         <f t="shared" si="15"/>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="Z5">
         <f t="shared" si="18"/>
-        <v>600</v>
+        <v>545</v>
       </c>
       <c r="AA5">
         <f t="shared" si="19"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="V6">
         <f t="shared" si="14"/>
-        <v>852</v>
+        <v>730</v>
       </c>
       <c r="W6">
         <f t="shared" si="15"/>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="Z6">
         <f t="shared" si="18"/>
-        <v>650</v>
+        <v>590</v>
       </c>
       <c r="AA6">
         <f t="shared" si="19"/>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="V7">
         <f t="shared" si="14"/>
-        <v>915</v>
+        <v>780</v>
       </c>
       <c r="W7">
         <f t="shared" si="15"/>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="Z7">
         <f t="shared" si="18"/>
-        <v>700</v>
+        <v>635</v>
       </c>
       <c r="AA7">
         <f t="shared" si="19"/>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="V8">
         <f t="shared" si="14"/>
-        <v>978</v>
+        <v>830</v>
       </c>
       <c r="W8">
         <f t="shared" si="15"/>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="Z8">
         <f t="shared" si="18"/>
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="AA8">
         <f t="shared" si="19"/>
@@ -8233,10 +8233,10 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="C9">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>166</v>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="V9">
         <f t="shared" si="14"/>
-        <v>1041</v>
+        <v>880</v>
       </c>
       <c r="W9">
         <f t="shared" si="15"/>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="18"/>
-        <v>800</v>
+        <v>725</v>
       </c>
       <c r="AA9">
         <f t="shared" si="19"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="V10">
         <f t="shared" si="14"/>
-        <v>1104</v>
+        <v>930</v>
       </c>
       <c r="W10">
         <f t="shared" si="15"/>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="Z10">
         <f t="shared" si="18"/>
-        <v>850</v>
+        <v>770</v>
       </c>
       <c r="AA10">
         <f t="shared" si="19"/>
@@ -8417,10 +8417,10 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="V11">
         <f t="shared" si="14"/>
-        <v>1167</v>
+        <v>980</v>
       </c>
       <c r="W11">
         <f t="shared" si="15"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="V12">
         <f t="shared" si="14"/>
-        <v>1230</v>
+        <v>1030</v>
       </c>
       <c r="W12">
         <f t="shared" si="15"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="V13">
         <f t="shared" si="14"/>
-        <v>1293</v>
+        <v>1080</v>
       </c>
       <c r="W13">
         <f t="shared" si="15"/>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="V14">
         <f t="shared" si="14"/>
-        <v>1356</v>
+        <v>1130</v>
       </c>
       <c r="W14">
         <f t="shared" si="15"/>
